--- a/artfynd/A 6108-2023 artfynd.xlsx
+++ b/artfynd/A 6108-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6108-2023 artfynd.xlsx
+++ b/artfynd/A 6108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104449393</v>
+        <v>104449376</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418188.408122587</v>
+        <v>418366</v>
       </c>
       <c r="R2" t="n">
-        <v>7018072.943679515</v>
+        <v>7018384</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104449298</v>
+        <v>104449379</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418152.1433075544</v>
+        <v>418359</v>
       </c>
       <c r="R3" t="n">
-        <v>7018755.833866266</v>
+        <v>7018387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,24 +840,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104449306</v>
+        <v>104449382</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418116.3208070688</v>
+        <v>418360</v>
       </c>
       <c r="R4" t="n">
-        <v>7018906.624424814</v>
+        <v>7018414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,24 +937,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104449305</v>
+        <v>104449384</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418113.1107625436</v>
+        <v>418265</v>
       </c>
       <c r="R5" t="n">
-        <v>7018904.455793464</v>
+        <v>7018346</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,24 +1034,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104449333</v>
+        <v>104449390</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418224.807980529</v>
+        <v>418166</v>
       </c>
       <c r="R6" t="n">
-        <v>7018298.906277624</v>
+        <v>7018080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,24 +1131,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104449307</v>
+        <v>104449393</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418106.0762497109</v>
+        <v>418189</v>
       </c>
       <c r="R7" t="n">
-        <v>7018911.38607322</v>
+        <v>7018073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,24 +1228,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,58 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104449297</v>
+        <v>104449365</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418163.1633477406</v>
+        <v>418265</v>
       </c>
       <c r="R8" t="n">
-        <v>7018746.101364438</v>
+        <v>7018346</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,24 +1325,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104449308</v>
+        <v>104449297</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1387,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1585,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418207.1051796933</v>
+        <v>418163</v>
       </c>
       <c r="R9" t="n">
-        <v>7019144.644948276</v>
+        <v>7018746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,24 +1430,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påbörjat bo?</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,6 +1461,1545 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104449298</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>418152</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7018756</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104449299</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>418113</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7018754</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104449305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>418113</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7018905</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104449306</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>418116</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7018906</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104449307</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>418106</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7018911</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104449308</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>418207</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7019144</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påbörjat bo?</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104449318</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>418361</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7018429</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104449321</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>418370</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7018433</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104449324</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>418364</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7018440</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104449327</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>418365</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7018433</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104449330</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>418357</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7018444</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104449333</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>418225</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7018299</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>104449356</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>418167</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7018086</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104449396</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>418159</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7018046</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6108-2023 artfynd.xlsx
+++ b/artfynd/A 6108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449376</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449379</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449384</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449390</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449393</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449365</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449297</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449298</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449299</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449308</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449318</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2341,6 +2421,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449321</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449324</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2561,6 +2651,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449327</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2671,6 +2766,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449330</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2781,6 +2881,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449333</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2891,6 +2996,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449356</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3000,8 +3110,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>